--- a/database/seeders/data/09_INFORMACION_ADMINISTRATIVA.xlsx
+++ b/database/seeders/data/09_INFORMACION_ADMINISTRATIVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56066FA-0422-4D58-B038-CBAE5E9D0088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90160794-5DC6-4615-9590-67A1525DEB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -931,6 +931,7 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -942,7 +943,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1167,11 +1167,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1179,11 +1179,11 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1236,11 +1236,11 @@
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
@@ -1291,12 +1291,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -1327,7 +1327,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C12" s="23"/>
+      <c r="C12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1352,19 +1352,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -1509,10 +1509,10 @@
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="21"/>
+      <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -1548,12 +1548,12 @@
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -1613,13 +1613,13 @@
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
@@ -1692,18 +1692,18 @@
     <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
@@ -1834,16 +1834,16 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
@@ -1950,16 +1950,16 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
@@ -2066,12 +2066,12 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
     </row>
     <row r="51" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
@@ -2161,19 +2161,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -2263,10 +2263,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2304,12 +2304,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2360,13 +2360,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2427,18 +2427,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2520,7 +2520,7 @@
     <col min="1" max="1" width="22.81640625" customWidth="1"/>
     <col min="2" max="2" width="26.6328125" customWidth="1"/>
     <col min="3" max="3" width="26.26953125" customWidth="1"/>
-    <col min="4" max="4" width="27.08984375" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="27.6328125" customWidth="1"/>
     <col min="6" max="6" width="23.90625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
@@ -2528,16 +2528,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2615,16 +2615,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">

--- a/database/seeders/data/09_INFORMACION_ADMINISTRATIVA.xlsx
+++ b/database/seeders/data/09_INFORMACION_ADMINISTRATIVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\ParquesEsp\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90160794-5DC6-4615-9590-67A1525DEB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722C18A9-BF6E-4FA2-B09B-527A1E6241D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,7 @@
     <sheet name="MULTAS" sheetId="5" r:id="rId5"/>
     <sheet name="AMONESTACIONES" sheetId="6" r:id="rId6"/>
     <sheet name="INCIDENTES DE VISITANTES" sheetId="7" r:id="rId7"/>
-    <sheet name="TIPOS DE ARCHIVO" sheetId="8" r:id="rId8"/>
-    <sheet name="ARCHIVOS DEL CLUB" sheetId="9" r:id="rId9"/>
-    <sheet name="REGLAS DEL CLUB" sheetId="10" r:id="rId10"/>
+    <sheet name="REGLAS DEL CLUB" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="160">
   <si>
     <t>INSTRUCCIONES DE CAPTURA</t>
   </si>
@@ -413,28 +411,10 @@
     </r>
   </si>
   <si>
-    <t>Folio o referencia de esta acta en el sistema anterior, si existe. Este folio se usa para relacionarla con ARCHIVOS DE ACTAS, MULTAS y AMONESTACIONES.</t>
-  </si>
-  <si>
     <t>Ver catálogo CLUBES en 02_CLUBES_Y_CONFIGURACION.</t>
   </si>
   <si>
     <t>Ver hoja SOCIOS en 03_SOCIOS.</t>
-  </si>
-  <si>
-    <t>Nombre del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido paterno del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Apellido materno del socio, para referencia visual.</t>
-  </si>
-  <si>
-    <t>Ver hoja MEMBRESIAS en 04_CUENTAS_Y_MEMBRESIAS. Junto con el número de socio, identifica la cuenta a la que pertenece el acta.</t>
-  </si>
-  <si>
-    <t>Descripción corta del tipo de falta (ej. Uso indebido de instalaciones, Conducta inapropiada).</t>
   </si>
   <si>
     <t>Detalle de lo ocurrido.</t>
@@ -469,9 +449,6 @@
     <t>Debe coincidir con un folio capturado en la hoja ACTAS.</t>
   </si>
   <si>
-    <t>Nombre o ruta del archivo/comprobante relacionado con el acta (ej. fotografía, reporte firmado). El archivo en sí se entrega aparte, aquí solo se captura la referencia.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -495,13 +472,7 @@
     <t>Debe coincidir con un folio capturado en la hoja ACTAS. Toda multa requiere un acta.</t>
   </si>
   <si>
-    <t>Importe de la multa en pesos (MXN).</t>
-  </si>
-  <si>
     <t>Concepto o motivo de la multa.</t>
-  </si>
-  <si>
-    <t>Fecha límite de pago, si aplica.</t>
   </si>
   <si>
     <r>
@@ -527,15 +498,6 @@
     <t>Debe coincidir con un folio capturado en la hoja ACTAS. Toda amonestación requiere un acta.</t>
   </si>
   <si>
-    <t>Tipo o nivel de amonestación (ej. Verbal, Escrita, Extrañamiento).</t>
-  </si>
-  <si>
-    <t>SÍ/NO. Si la amonestación incluye suspensión temporal de derechos como socio.</t>
-  </si>
-  <si>
-    <t>Solo si TIENE SUSPENSIÓN es SÍ.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -556,107 +518,7 @@
     </r>
   </si>
   <si>
-    <t>Nombre del visitante involucrado en el incidente.</t>
-  </si>
-  <si>
-    <t>Apellido del visitante involucrado en el incidente.</t>
-  </si>
-  <si>
     <t>Si se conoce.</t>
-  </si>
-  <si>
-    <t>Solo si el incidente está ligado a un pase diario programado capturado en 08_RESERVACIONES_Y_ACCESOS. Déjalo vacío si no aplica o si el pase no se va a migrar.</t>
-  </si>
-  <si>
-    <t>Descripción corta del tipo de incidente (ej. Acceso no autorizado, Mal comportamiento).</t>
-  </si>
-  <si>
-    <t>Si se cobró algún importe al visitante o al socio responsable por el incidente.</t>
-  </si>
-  <si>
-    <t>Correo del usuario del sistema (staff del club) que registró el incidente.</t>
-  </si>
-  <si>
-    <t>Fecha y hora en que ocurrió o se registró el incidente. Formato AAAA-MM-DD HH:MM.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">6. TIPOS DE ARCHIVO   </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FFB0BEC5"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(sin tabla en el sistema todavía)</t>
-    </r>
-  </si>
-  <si>
-    <t>Clave única para identificar el tipo de archivo (ej. ACTA-EVIDENCIA, CLUB-REGLAMENTO).</t>
-  </si>
-  <si>
-    <t>Nombre visible del tipo de archivo.</t>
-  </si>
-  <si>
-    <t>Para qué se usa este tipo de archivo.</t>
-  </si>
-  <si>
-    <t>Sección del sistema donde aplica (ej. Actas, Club).</t>
-  </si>
-  <si>
-    <t>SÍ/NO. Si el sistema debe exigir este archivo.</t>
-  </si>
-  <si>
-    <t>SÍ/NO.</t>
-  </si>
-  <si>
-    <t>Extensiones permitidas, separadas por coma (ej. PDF, JPG, PNG).</t>
-  </si>
-  <si>
-    <t>Tamaño máximo permitido por archivo, en megabytes.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">7. ARCHIVOS DEL CLUB   </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FFB0BEC5"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>(sin tabla en el sistema todavía)</t>
-    </r>
-  </si>
-  <si>
-    <t>Ver hoja TIPOS DE ARCHIVO. Debe usar el MÓDULO 'Club'.</t>
-  </si>
-  <si>
-    <t>Nombre visible del archivo (ej. Reglamento interno 2026).</t>
-  </si>
-  <si>
-    <t>Nombre o ruta del archivo. El archivo en sí se entrega aparte, aquí solo se captura la referencia.</t>
-  </si>
-  <si>
-    <t>Extensión o formato del archivo (ej. PDF, JPG).</t>
-  </si>
-  <si>
-    <t>Número para ordenar los archivos si se muestran en una lista.</t>
   </si>
   <si>
     <r>
@@ -679,10 +541,79 @@
     </r>
   </si>
   <si>
-    <t>Número máximo de reservaciones activas que puede tener un socio a la vez en este club.</t>
-  </si>
-  <si>
-    <t>Con cuántos días de anticipación máximo se puede reservar.</t>
+    <t>Folio o referencia de esta acta</t>
+  </si>
+  <si>
+    <t>Nombre del socio</t>
+  </si>
+  <si>
+    <t>Apellido paterno del socio</t>
+  </si>
+  <si>
+    <t>Apellido materno del socio</t>
+  </si>
+  <si>
+    <t>Ver hoja MEMBRESIAS en 04_CUENTAS_Y_MEMBRESIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Uso indebido de instalaciones, Conducta inapropiada</t>
+  </si>
+  <si>
+    <t>FOLIO O REFERENCIA DEL ACTA</t>
+  </si>
+  <si>
+    <t>Nombre o ruta del archivo</t>
+  </si>
+  <si>
+    <t>Importe  (MXN).</t>
+  </si>
+  <si>
+    <t>Fecha límite de pago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo o nivel de amonestación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SÍ/NO. Si la amonestación incluye suspensión temporal </t>
+  </si>
+  <si>
+    <t>Solo si TIENE SUSPENSIÓN es si</t>
+  </si>
+  <si>
+    <t>solo si TIENE SUSPENSIÓN es si</t>
+  </si>
+  <si>
+    <t>Nombre del visitante</t>
+  </si>
+  <si>
+    <t>Apellido del visitante</t>
+  </si>
+  <si>
+    <t>Solo si el incidente está ligado a un pase diario programado capturado en 08_RESERVACIONES_Y_ACCESOS</t>
+  </si>
+  <si>
+    <t>Descripción corta del tipo de incidente</t>
+  </si>
+  <si>
+    <t>Si se cobró algun importe al visitante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correo del usuario del sistema </t>
+  </si>
+  <si>
+    <t>Formato AAAA-MM-DD HH:MM.</t>
+  </si>
+  <si>
+    <t>Ver catálogo CLUBES en 02_CLUBES_Y_CONFIGURACION</t>
+  </si>
+  <si>
+    <t>Número máximo de reservaciones activas que puede tener un socio a la vez en este club</t>
+  </si>
+  <si>
+    <t>Con cuántos días de anticipación maximo se puede reservar</t>
+  </si>
+  <si>
+    <t>SI/NO</t>
   </si>
 </sst>
 </file>
@@ -694,7 +625,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -768,8 +699,12 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -819,6 +754,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECF0F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -888,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -932,6 +873,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -943,6 +888,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1167,11 +1113,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1179,11 +1125,11 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1236,11 +1182,11 @@
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
@@ -1276,65 +1222,6 @@
     <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="40.453125" customWidth="1"/>
-    <col min="2" max="2" width="40.26953125" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="37.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-    </row>
-    <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C12" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="146" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1352,19 +1239,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -1509,10 +1396,10 @@
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="24"/>
     </row>
     <row r="9" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -1547,13 +1434,16 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C14" s="16"/>
+    </row>
     <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -1613,13 +1503,13 @@
     </row>
     <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
@@ -1692,18 +1582,18 @@
     <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
@@ -1834,16 +1724,16 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
@@ -1950,16 +1840,16 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
@@ -2066,12 +1956,12 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
     </row>
     <row r="51" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
@@ -2141,6 +2031,7 @@
     <mergeCell ref="A36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="146" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2151,29 +2042,31 @@
   <cols>
     <col min="1" max="1" width="50.1796875" customWidth="1"/>
     <col min="2" max="2" width="29.81640625" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="28.08984375" customWidth="1"/>
-    <col min="7" max="7" width="33.08984375" customWidth="1"/>
-    <col min="8" max="8" width="23.36328125" customWidth="1"/>
-    <col min="9" max="11" width="16" customWidth="1"/>
+    <col min="3" max="3" width="33.08984375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="29.453125" customWidth="1"/>
+    <col min="5" max="5" width="28.54296875" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="28.08984375" customWidth="1"/>
+    <col min="8" max="8" width="30.90625" customWidth="1"/>
+    <col min="9" max="9" width="33.08984375" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="21.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
     </row>
     <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
@@ -2182,20 +2075,20 @@
       <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>27</v>
@@ -2212,37 +2105,37 @@
     </row>
     <row r="3" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2263,14 +2156,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="23"/>
+      <c r="A1" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="25"/>
     </row>
     <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>60</v>
@@ -2278,10 +2171,10 @@
     </row>
     <row r="3" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2304,12 +2197,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="A1" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2327,16 +2220,16 @@
     </row>
     <row r="3" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2360,13 +2253,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="A1" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2387,19 +2280,19 @@
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2421,24 +2314,24 @@
     <col min="4" max="4" width="29.7265625" customWidth="1"/>
     <col min="5" max="5" width="64.36328125" customWidth="1"/>
     <col min="6" max="6" width="34.08984375" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="56.26953125" customWidth="1"/>
+    <col min="8" max="8" width="35.7265625" customWidth="1"/>
     <col min="9" max="10" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="A1" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
@@ -2474,34 +2367,34 @@
     </row>
     <row r="3" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2513,175 +2406,60 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.81640625" customWidth="1"/>
-    <col min="2" max="2" width="26.6328125" customWidth="1"/>
-    <col min="3" max="3" width="26.26953125" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="27.6328125" customWidth="1"/>
-    <col min="6" max="6" width="23.90625" customWidth="1"/>
-    <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" customWidth="1"/>
+    <col min="1" max="1" width="40.453125" customWidth="1"/>
+    <col min="2" max="2" width="40.26953125" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="37.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>161</v>
-      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="28.90625" customWidth="1"/>
-    <col min="2" max="2" width="35.36328125" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="47.1796875" customWidth="1"/>
-    <col min="5" max="5" width="19.453125" customWidth="1"/>
-    <col min="6" max="6" width="35.08984375" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="28.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="2" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>167</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="146" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>